--- a/docs/StructureDefinition-DIPSPractitioner.xlsx
+++ b/docs/StructureDefinition-DIPSPractitioner.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:16:58+00:00</t>
+    <t>2026-09-08T11:30:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,7 +449,7 @@
     <t>specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerSpecialist}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerSpecialist}
 </t>
   </si>
   <si>
@@ -469,7 +469,7 @@
     <t>isASpecialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/IsSpecialistExtension}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/IsSpecialistExtension}
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-DIPSPractitioner.xlsx
+++ b/docs/StructureDefinition-DIPSPractitioner.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:30:20+00:00</t>
+    <t>2026-09-15T05:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPractitioner.xlsx
+++ b/docs/StructureDefinition-DIPSPractitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4047" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4047" uniqueCount="557">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T05:06:55+00:00</t>
+    <t>2026-09-17T19:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -996,6 +996,10 @@
   </si>
   <si>
     <t>middlename</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mellomnavn
+</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://hl7.no/fhir/StructureDefinition/no-basis-middlename}
@@ -9061,14 +9065,14 @@
         <v>314</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>75</v>
+        <v>315</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -9080,13 +9084,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9166,10 +9170,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9195,16 +9199,16 @@
         <v>106</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>75</v>
@@ -9232,10 +9236,10 @@
         <v>180</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>75</v>
@@ -9253,7 +9257,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9268,13 +9272,13 @@
         <v>98</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>75</v>
@@ -9282,10 +9286,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9311,16 +9315,16 @@
         <v>165</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -9369,7 +9373,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9384,10 +9388,10 @@
         <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>75</v>
@@ -9398,14 +9402,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9427,13 +9431,13 @@
         <v>165</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9483,7 +9487,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9498,13 +9502,13 @@
         <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>75</v>
@@ -9512,14 +9516,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9541,13 +9545,13 @@
         <v>165</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9597,7 +9601,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -9612,13 +9616,13 @@
         <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>75</v>
@@ -9626,10 +9630,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9655,10 +9659,10 @@
         <v>165</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9709,7 +9713,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9724,13 +9728,13 @@
         <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>75</v>
@@ -9738,10 +9742,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9767,10 +9771,10 @@
         <v>165</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9821,7 +9825,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9836,10 +9840,10 @@
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>75</v>
@@ -9850,10 +9854,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9879,14 +9883,14 @@
         <v>216</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9935,7 +9939,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9950,10 +9954,10 @@
         <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>222</v>
@@ -9964,10 +9968,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9990,19 +9994,19 @@
         <v>87</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -10051,7 +10055,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10066,13 +10070,13 @@
         <v>98</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>75</v>
@@ -10080,10 +10084,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10106,19 +10110,19 @@
         <v>87</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10167,7 +10171,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10182,13 +10186,13 @@
         <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>75</v>
@@ -10196,10 +10200,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10225,14 +10229,14 @@
         <v>106</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -10260,10 +10264,10 @@
         <v>180</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>75</v>
@@ -10281,7 +10285,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10296,13 +10300,13 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>75</v>
@@ -10310,10 +10314,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10336,17 +10340,17 @@
         <v>87</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -10395,7 +10399,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10410,13 +10414,13 @@
         <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>75</v>
@@ -10424,10 +10428,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10450,17 +10454,17 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>75</v>
@@ -10509,7 +10513,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10527,10 +10531,10 @@
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>75</v>
@@ -10538,10 +10542,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10564,13 +10568,13 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10621,7 +10625,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10636,13 +10640,13 @@
         <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>75</v>
@@ -10650,10 +10654,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10762,10 +10766,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10876,14 +10880,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10905,10 +10909,10 @@
         <v>131</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>151</v>
@@ -10963,7 +10967,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10992,10 +10996,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11021,14 +11025,14 @@
         <v>155</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>75</v>
@@ -11077,7 +11081,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11095,7 +11099,7 @@
         <v>75</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>75</v>
@@ -11106,10 +11110,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11135,10 +11139,10 @@
         <v>186</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11165,13 +11169,13 @@
         <v>75</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>75</v>
@@ -11189,7 +11193,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>86</v>
@@ -11207,10 +11211,10 @@
         <v>75</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>75</v>
@@ -11218,10 +11222,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11330,10 +11334,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11444,10 +11448,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11470,19 +11474,19 @@
         <v>87</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>75</v>
@@ -11529,7 +11533,7 @@
         <v>135</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11544,10 +11548,10 @@
         <v>98</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>75</v>
@@ -11558,13 +11562,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>75</v>
@@ -11586,19 +11590,19 @@
         <v>87</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>75</v>
@@ -11627,7 +11631,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>75</v>
@@ -11645,7 +11649,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -11660,10 +11664,10 @@
         <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>75</v>
@@ -11674,10 +11678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11786,10 +11790,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11900,10 +11904,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11929,23 +11933,23 @@
         <v>100</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>75</v>
@@ -11987,7 +11991,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12002,10 +12006,10 @@
         <v>98</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>75</v>
@@ -12016,10 +12020,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12045,13 +12049,13 @@
         <v>165</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12101,7 +12105,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12116,10 +12120,10 @@
         <v>98</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>75</v>
@@ -12130,10 +12134,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12159,14 +12163,14 @@
         <v>106</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>75</v>
@@ -12215,7 +12219,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12230,10 +12234,10 @@
         <v>98</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>75</v>
@@ -12244,10 +12248,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12273,14 +12277,14 @@
         <v>165</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>75</v>
@@ -12329,7 +12333,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12344,10 +12348,10 @@
         <v>98</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>75</v>
@@ -12358,10 +12362,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12387,16 +12391,16 @@
         <v>294</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>75</v>
@@ -12445,7 +12449,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12460,10 +12464,10 @@
         <v>98</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>75</v>
@@ -12474,13 +12478,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>75</v>
@@ -12502,19 +12506,19 @@
         <v>87</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -12543,7 +12547,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>75</v>
@@ -12561,7 +12565,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12576,10 +12580,10 @@
         <v>98</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>75</v>
@@ -12590,10 +12594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12702,10 +12706,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12816,10 +12820,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12845,23 +12849,23 @@
         <v>100</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>75</v>
@@ -12903,7 +12907,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -12918,10 +12922,10 @@
         <v>98</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>75</v>
@@ -12932,10 +12936,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12961,13 +12965,13 @@
         <v>165</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13017,7 +13021,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13032,10 +13036,10 @@
         <v>98</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>75</v>
@@ -13046,10 +13050,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13075,14 +13079,14 @@
         <v>106</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>75</v>
@@ -13131,7 +13135,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13146,10 +13150,10 @@
         <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>75</v>
@@ -13160,10 +13164,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13189,14 +13193,14 @@
         <v>165</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>75</v>
@@ -13245,7 +13249,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13260,10 +13264,10 @@
         <v>98</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>75</v>
@@ -13274,10 +13278,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13303,16 +13307,16 @@
         <v>294</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>75</v>
@@ -13361,7 +13365,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13376,10 +13380,10 @@
         <v>98</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>75</v>
@@ -13390,13 +13394,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>75</v>
@@ -13418,19 +13422,19 @@
         <v>87</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>75</v>
@@ -13459,7 +13463,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>75</v>
@@ -13477,7 +13481,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13492,10 +13496,10 @@
         <v>98</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>75</v>
@@ -13506,10 +13510,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13618,10 +13622,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13732,10 +13736,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13761,23 +13765,23 @@
         <v>100</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>75</v>
@@ -13819,7 +13823,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -13834,10 +13838,10 @@
         <v>98</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>75</v>
@@ -13848,10 +13852,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13877,13 +13881,13 @@
         <v>165</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13933,7 +13937,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -13948,10 +13952,10 @@
         <v>98</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>75</v>
@@ -13962,10 +13966,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13991,14 +13995,14 @@
         <v>106</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>75</v>
@@ -14047,7 +14051,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -14062,10 +14066,10 @@
         <v>98</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>75</v>
@@ -14076,10 +14080,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14105,14 +14109,14 @@
         <v>165</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>75</v>
@@ -14161,7 +14165,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14176,10 +14180,10 @@
         <v>98</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>75</v>
@@ -14190,10 +14194,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14219,16 +14223,16 @@
         <v>294</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>75</v>
@@ -14277,7 +14281,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14292,10 +14296,10 @@
         <v>98</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>75</v>
@@ -14306,10 +14310,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14335,16 +14339,16 @@
         <v>165</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>75</v>
@@ -14393,7 +14397,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14408,10 +14412,10 @@
         <v>98</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>75</v>
@@ -14422,10 +14426,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14451,14 +14455,14 @@
         <v>216</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>75</v>
@@ -14507,7 +14511,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14525,10 +14529,10 @@
         <v>75</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>75</v>
@@ -14536,10 +14540,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14565,10 +14569,10 @@
         <v>224</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14619,7 +14623,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14637,7 +14641,7 @@
         <v>75</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>75</v>
@@ -14648,10 +14652,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14677,16 +14681,16 @@
         <v>186</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>75</v>
@@ -14735,7 +14739,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14750,13 +14754,13 @@
         <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>75</v>

--- a/docs/StructureDefinition-DIPSPractitioner.xlsx
+++ b/docs/StructureDefinition-DIPSPractitioner.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T19:39:02+00:00</t>
+    <t>2026-09-18T19:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPractitioner.xlsx
+++ b/docs/StructureDefinition-DIPSPractitioner.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T19:41:15+00:00</t>
+    <t>2026-09-29T03:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPractitioner.xlsx
+++ b/docs/StructureDefinition-DIPSPractitioner.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T03:57:01+00:00</t>
+    <t>2026-09-29T04:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
